--- a/artfynd/A 60977-2025 artfynd.xlsx
+++ b/artfynd/A 60977-2025 artfynd.xlsx
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130886838</v>
+        <v>130886779</v>
       </c>
       <c r="B11" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,19 +1559,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1579,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434362</v>
+        <v>434359</v>
       </c>
       <c r="R11" t="n">
-        <v>7052349</v>
+        <v>7052173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1615,6 +1619,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1641,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130886779</v>
+        <v>130886838</v>
       </c>
       <c r="B12" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,23 +1661,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434359</v>
+        <v>434362</v>
       </c>
       <c r="R12" t="n">
-        <v>7052173</v>
+        <v>7052349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1712,11 +1717,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1743,10 +1743,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130886839</v>
+        <v>130886774</v>
       </c>
       <c r="B13" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1754,19 +1754,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1774,10 +1778,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434382</v>
+        <v>434519</v>
       </c>
       <c r="R13" t="n">
-        <v>7052442</v>
+        <v>7052220</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1810,6 +1814,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1836,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130886774</v>
+        <v>130886839</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1847,23 +1856,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1871,10 +1876,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434519</v>
+        <v>434382</v>
       </c>
       <c r="R14" t="n">
-        <v>7052220</v>
+        <v>7052442</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1907,11 +1912,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130886759</v>
+        <v>130886777</v>
       </c>
       <c r="B15" t="n">
         <v>57864</v>
@@ -1967,24 +1967,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434213</v>
+        <v>434295</v>
       </c>
       <c r="R15" t="n">
-        <v>7052218</v>
+        <v>7052449</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2021,7 +2013,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,7 +2040,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130886777</v>
+        <v>130886759</v>
       </c>
       <c r="B16" t="n">
         <v>57864</v>
@@ -2077,16 +2069,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434295</v>
+        <v>434213</v>
       </c>
       <c r="R16" t="n">
-        <v>7052449</v>
+        <v>7052218</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2354,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130886804</v>
+        <v>130886806</v>
       </c>
       <c r="B19" t="n">
         <v>57864</v>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433939</v>
+        <v>433991</v>
       </c>
       <c r="R19" t="n">
-        <v>7052224</v>
+        <v>7052181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,7 +2456,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130886806</v>
+        <v>130886804</v>
       </c>
       <c r="B20" t="n">
         <v>57864</v>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433991</v>
+        <v>433939</v>
       </c>
       <c r="R20" t="n">
-        <v>7052181</v>
+        <v>7052224</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130886831</v>
+        <v>130886801</v>
       </c>
       <c r="B22" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434871</v>
+        <v>434001</v>
       </c>
       <c r="R22" t="n">
-        <v>7051709</v>
+        <v>7052192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2762,10 +2762,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130886836</v>
+        <v>130886793</v>
       </c>
       <c r="B23" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2773,19 +2773,23 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2793,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434854</v>
+        <v>434143</v>
       </c>
       <c r="R23" t="n">
-        <v>7051718</v>
+        <v>7052197</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,6 +2833,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,7 +2864,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130886818</v>
+        <v>130886794</v>
       </c>
       <c r="B24" t="n">
         <v>57864</v>
@@ -2890,10 +2899,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434272</v>
+        <v>434140</v>
       </c>
       <c r="R24" t="n">
-        <v>7052031</v>
+        <v>7052192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,7 +2939,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2957,7 +2966,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130886794</v>
+        <v>130886818</v>
       </c>
       <c r="B25" t="n">
         <v>57864</v>
@@ -2992,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434140</v>
+        <v>434272</v>
       </c>
       <c r="R25" t="n">
-        <v>7052192</v>
+        <v>7052031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,7 +3041,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3059,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130886801</v>
+        <v>130886836</v>
       </c>
       <c r="B26" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,23 +3079,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3094,10 +3099,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434001</v>
+        <v>434854</v>
       </c>
       <c r="R26" t="n">
-        <v>7052192</v>
+        <v>7051718</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,11 +3135,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3161,10 +3161,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130886793</v>
+        <v>130886831</v>
       </c>
       <c r="B27" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3172,16 +3172,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434143</v>
+        <v>434871</v>
       </c>
       <c r="R27" t="n">
-        <v>7052197</v>
+        <v>7051709</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3365,7 +3365,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130886787</v>
+        <v>130886827</v>
       </c>
       <c r="B29" t="n">
         <v>57864</v>
@@ -3400,10 +3400,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434193</v>
+        <v>434485</v>
       </c>
       <c r="R29" t="n">
-        <v>7052219</v>
+        <v>7051846</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3467,7 +3467,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130886827</v>
+        <v>130886787</v>
       </c>
       <c r="B30" t="n">
         <v>57864</v>
@@ -3502,10 +3502,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434485</v>
+        <v>434193</v>
       </c>
       <c r="R30" t="n">
-        <v>7051846</v>
+        <v>7052219</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3569,7 +3569,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130886799</v>
+        <v>130886816</v>
       </c>
       <c r="B31" t="n">
         <v>57864</v>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434100</v>
+        <v>434134</v>
       </c>
       <c r="R31" t="n">
-        <v>7052230</v>
+        <v>7052114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3671,7 +3671,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130886816</v>
+        <v>130886766</v>
       </c>
       <c r="B32" t="n">
         <v>57864</v>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434134</v>
+        <v>434506</v>
       </c>
       <c r="R32" t="n">
-        <v>7052114</v>
+        <v>7052005</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130886766</v>
+        <v>130886799</v>
       </c>
       <c r="B33" t="n">
         <v>57864</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434506</v>
+        <v>434100</v>
       </c>
       <c r="R33" t="n">
-        <v>7052005</v>
+        <v>7052230</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4079,7 +4079,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130886810</v>
+        <v>130886822</v>
       </c>
       <c r="B36" t="n">
         <v>57864</v>
@@ -4108,16 +4108,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434078</v>
+        <v>434465</v>
       </c>
       <c r="R36" t="n">
-        <v>7052137</v>
+        <v>7051934</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4154,7 +4162,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Möjligt påbörjat gammalt bohål ca 1,7 m upp i rötad gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4181,7 +4189,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130886822</v>
+        <v>130886810</v>
       </c>
       <c r="B37" t="n">
         <v>57864</v>
@@ -4210,24 +4218,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434465</v>
+        <v>434078</v>
       </c>
       <c r="R37" t="n">
-        <v>7051934</v>
+        <v>7052137</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Möjligt påbörjat gammalt bohål ca 1,7 m upp i rötad gran</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4393,10 +4393,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130886845</v>
+        <v>130886805</v>
       </c>
       <c r="B39" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4404,19 +4404,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4424,10 +4428,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434162</v>
+        <v>433991</v>
       </c>
       <c r="R39" t="n">
-        <v>7052165</v>
+        <v>7052188</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4460,6 +4464,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4583,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130886805</v>
+        <v>130886845</v>
       </c>
       <c r="B41" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4594,23 +4603,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4618,10 +4623,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433991</v>
+        <v>434162</v>
       </c>
       <c r="R41" t="n">
-        <v>7052188</v>
+        <v>7052165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4654,11 +4659,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4685,10 +4685,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130886828</v>
+        <v>130886846</v>
       </c>
       <c r="B42" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4696,23 +4696,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4720,10 +4716,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434679</v>
+        <v>434095</v>
       </c>
       <c r="R42" t="n">
-        <v>7051828</v>
+        <v>7052227</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4756,11 +4752,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4787,10 +4778,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130886846</v>
+        <v>130886786</v>
       </c>
       <c r="B43" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4798,19 +4789,23 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -4818,10 +4813,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434095</v>
+        <v>434196</v>
       </c>
       <c r="R43" t="n">
-        <v>7052227</v>
+        <v>7052215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4854,6 +4849,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4880,7 +4880,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130886786</v>
+        <v>130886798</v>
       </c>
       <c r="B44" t="n">
         <v>57864</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434196</v>
+        <v>434094</v>
       </c>
       <c r="R44" t="n">
-        <v>7052215</v>
+        <v>7052167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4982,7 +4982,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130886798</v>
+        <v>130886828</v>
       </c>
       <c r="B45" t="n">
         <v>57864</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434094</v>
+        <v>434679</v>
       </c>
       <c r="R45" t="n">
-        <v>7052167</v>
+        <v>7051828</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5186,7 +5186,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130886768</v>
+        <v>130886802</v>
       </c>
       <c r="B47" t="n">
         <v>57864</v>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434508</v>
+        <v>434012</v>
       </c>
       <c r="R47" t="n">
-        <v>7052004</v>
+        <v>7052200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5288,7 +5288,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130886830</v>
+        <v>130886773</v>
       </c>
       <c r="B48" t="n">
         <v>57864</v>
@@ -5323,10 +5323,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434860</v>
+        <v>434554</v>
       </c>
       <c r="R48" t="n">
-        <v>7051773</v>
+        <v>7052008</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5363,7 +5363,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5390,7 +5390,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130886773</v>
+        <v>130886768</v>
       </c>
       <c r="B49" t="n">
         <v>57864</v>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434554</v>
+        <v>434508</v>
       </c>
       <c r="R49" t="n">
-        <v>7052008</v>
+        <v>7052004</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5492,7 +5492,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130886802</v>
+        <v>130886830</v>
       </c>
       <c r="B50" t="n">
         <v>57864</v>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434012</v>
+        <v>434860</v>
       </c>
       <c r="R50" t="n">
-        <v>7052200</v>
+        <v>7051773</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130886811</v>
+        <v>130886837</v>
       </c>
       <c r="B51" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5605,23 +5605,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5629,10 +5625,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434077</v>
+        <v>434513</v>
       </c>
       <c r="R51" t="n">
-        <v>7052133</v>
+        <v>7052004</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5665,11 +5661,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5798,7 +5789,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130886826</v>
+        <v>130886765</v>
       </c>
       <c r="B53" t="n">
         <v>57864</v>
@@ -5833,10 +5824,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434489</v>
+        <v>434505</v>
       </c>
       <c r="R53" t="n">
-        <v>7051863</v>
+        <v>7052005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5873,7 +5864,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5900,7 +5891,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130886765</v>
+        <v>130886788</v>
       </c>
       <c r="B54" t="n">
         <v>57864</v>
@@ -5935,10 +5926,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434505</v>
+        <v>434171</v>
       </c>
       <c r="R54" t="n">
-        <v>7052005</v>
+        <v>7052213</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5975,7 +5966,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6002,10 +5993,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130886837</v>
+        <v>130886826</v>
       </c>
       <c r="B55" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6013,19 +6004,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6033,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434513</v>
+        <v>434489</v>
       </c>
       <c r="R55" t="n">
-        <v>7052004</v>
+        <v>7051863</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6069,6 +6064,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6095,7 +6095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130886788</v>
+        <v>130886811</v>
       </c>
       <c r="B56" t="n">
         <v>57864</v>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434171</v>
+        <v>434077</v>
       </c>
       <c r="R56" t="n">
-        <v>7052213</v>
+        <v>7052133</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6299,7 +6299,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130886814</v>
+        <v>130886771</v>
       </c>
       <c r="B58" t="n">
         <v>57864</v>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434117</v>
+        <v>434495</v>
       </c>
       <c r="R58" t="n">
-        <v>7052108</v>
+        <v>7052002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6401,7 +6401,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130886781</v>
+        <v>130886815</v>
       </c>
       <c r="B59" t="n">
         <v>57864</v>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434196</v>
+        <v>434133</v>
       </c>
       <c r="R59" t="n">
-        <v>7052172</v>
+        <v>7052112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130886771</v>
+        <v>130886814</v>
       </c>
       <c r="B60" t="n">
         <v>57864</v>
@@ -6538,10 +6538,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434495</v>
+        <v>434117</v>
       </c>
       <c r="R60" t="n">
-        <v>7052002</v>
+        <v>7052108</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6605,7 +6605,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130886815</v>
+        <v>130886781</v>
       </c>
       <c r="B61" t="n">
         <v>57864</v>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434133</v>
+        <v>434196</v>
       </c>
       <c r="R61" t="n">
-        <v>7052112</v>
+        <v>7052172</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130886782</v>
+        <v>130886817</v>
       </c>
       <c r="B62" t="n">
         <v>57864</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434188</v>
+        <v>434240</v>
       </c>
       <c r="R62" t="n">
-        <v>7052189</v>
+        <v>7052045</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6809,7 +6809,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130886797</v>
+        <v>130886782</v>
       </c>
       <c r="B63" t="n">
         <v>57864</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434118</v>
+        <v>434188</v>
       </c>
       <c r="R63" t="n">
-        <v>7052153</v>
+        <v>7052189</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6884,7 +6884,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6911,7 +6911,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130886817</v>
+        <v>130886797</v>
       </c>
       <c r="B64" t="n">
         <v>57864</v>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434240</v>
+        <v>434118</v>
       </c>
       <c r="R64" t="n">
-        <v>7052045</v>
+        <v>7052153</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6986,7 +6986,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7115,7 +7115,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130886829</v>
+        <v>130886795</v>
       </c>
       <c r="B66" t="n">
         <v>57864</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434697</v>
+        <v>434130</v>
       </c>
       <c r="R66" t="n">
-        <v>7051780</v>
+        <v>7052154</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,7 +7217,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130886803</v>
+        <v>130886829</v>
       </c>
       <c r="B67" t="n">
         <v>57864</v>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433904</v>
+        <v>434697</v>
       </c>
       <c r="R67" t="n">
-        <v>7052250</v>
+        <v>7051780</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7319,7 +7319,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130886795</v>
+        <v>130886803</v>
       </c>
       <c r="B68" t="n">
         <v>57864</v>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434130</v>
+        <v>433904</v>
       </c>
       <c r="R68" t="n">
-        <v>7052154</v>
+        <v>7052250</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7421,7 +7421,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130886807</v>
+        <v>130886819</v>
       </c>
       <c r="B69" t="n">
         <v>57864</v>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434035</v>
+        <v>434379</v>
       </c>
       <c r="R69" t="n">
-        <v>7052164</v>
+        <v>7051966</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7523,7 +7523,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130886819</v>
+        <v>130886807</v>
       </c>
       <c r="B70" t="n">
         <v>57864</v>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434379</v>
+        <v>434035</v>
       </c>
       <c r="R70" t="n">
-        <v>7051966</v>
+        <v>7052164</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7829,7 +7829,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130886813</v>
+        <v>130886823</v>
       </c>
       <c r="B73" t="n">
         <v>57864</v>
@@ -7864,10 +7864,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434112</v>
+        <v>434499</v>
       </c>
       <c r="R73" t="n">
-        <v>7052117</v>
+        <v>7051916</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130886821</v>
+        <v>130886813</v>
       </c>
       <c r="B74" t="n">
         <v>57864</v>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434468</v>
+        <v>434112</v>
       </c>
       <c r="R74" t="n">
-        <v>7051906</v>
+        <v>7052117</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8135,7 +8135,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130886789</v>
+        <v>130886821</v>
       </c>
       <c r="B76" t="n">
         <v>57864</v>
@@ -8170,10 +8170,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434159</v>
+        <v>434468</v>
       </c>
       <c r="R76" t="n">
-        <v>7052197</v>
+        <v>7051906</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130886823</v>
+        <v>130886789</v>
       </c>
       <c r="B77" t="n">
         <v>57864</v>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434499</v>
+        <v>434159</v>
       </c>
       <c r="R77" t="n">
-        <v>7051916</v>
+        <v>7052197</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8312,7 +8312,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 60977-2025 artfynd.xlsx
+++ b/artfynd/A 60977-2025 artfynd.xlsx
@@ -2558,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130886836</v>
+        <v>130886831</v>
       </c>
       <c r="B21" t="n">
-        <v>91829</v>
+        <v>57881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,19 +2569,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2589,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434854</v>
+        <v>434871</v>
       </c>
       <c r="R21" t="n">
-        <v>7051718</v>
+        <v>7051709</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2625,6 +2629,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2651,10 +2660,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130886792</v>
+        <v>130886836</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2662,23 +2671,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2686,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434158</v>
+        <v>434854</v>
       </c>
       <c r="R22" t="n">
-        <v>7052168</v>
+        <v>7051718</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,11 +2727,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2753,7 +2753,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130886801</v>
+        <v>130886792</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434001</v>
+        <v>434158</v>
       </c>
       <c r="R23" t="n">
-        <v>7052192</v>
+        <v>7052168</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,7 +2855,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130886793</v>
+        <v>130886801</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -2890,10 +2890,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434143</v>
+        <v>434001</v>
       </c>
       <c r="R24" t="n">
-        <v>7052197</v>
+        <v>7052192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2957,7 +2957,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130886794</v>
+        <v>130886793</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -2992,10 +2992,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434140</v>
+        <v>434143</v>
       </c>
       <c r="R25" t="n">
-        <v>7052192</v>
+        <v>7052197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3059,7 +3059,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130886818</v>
+        <v>130886794</v>
       </c>
       <c r="B26" t="n">
         <v>57884</v>
@@ -3094,10 +3094,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434272</v>
+        <v>434140</v>
       </c>
       <c r="R26" t="n">
-        <v>7052031</v>
+        <v>7052192</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3161,10 +3161,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130886831</v>
+        <v>130886818</v>
       </c>
       <c r="B27" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3172,16 +3172,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434871</v>
+        <v>434272</v>
       </c>
       <c r="R27" t="n">
-        <v>7051709</v>
+        <v>7052031</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130886845</v>
+        <v>130886835</v>
       </c>
       <c r="B38" t="n">
-        <v>91829</v>
+        <v>91805</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4302,19 +4302,23 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4322,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434162</v>
+        <v>434666</v>
       </c>
       <c r="R38" t="n">
-        <v>7052165</v>
+        <v>7051843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4384,10 +4388,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130886835</v>
+        <v>130886845</v>
       </c>
       <c r="B39" t="n">
-        <v>91805</v>
+        <v>91829</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4395,23 +4399,19 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434666</v>
+        <v>434162</v>
       </c>
       <c r="R39" t="n">
-        <v>7051843</v>
+        <v>7052165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4685,10 +4685,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130886786</v>
+        <v>130886846</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4696,23 +4696,19 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4720,10 +4716,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434196</v>
+        <v>434095</v>
       </c>
       <c r="R42" t="n">
-        <v>7052215</v>
+        <v>7052227</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4756,11 +4752,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4787,7 +4778,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130886798</v>
+        <v>130886786</v>
       </c>
       <c r="B43" t="n">
         <v>57884</v>
@@ -4822,10 +4813,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434094</v>
+        <v>434196</v>
       </c>
       <c r="R43" t="n">
-        <v>7052167</v>
+        <v>7052215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4862,7 +4853,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4889,7 +4880,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130886828</v>
+        <v>130886798</v>
       </c>
       <c r="B44" t="n">
         <v>57884</v>
@@ -4924,10 +4915,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434679</v>
+        <v>434094</v>
       </c>
       <c r="R44" t="n">
-        <v>7051828</v>
+        <v>7052167</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4991,10 +4982,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130886846</v>
+        <v>130886828</v>
       </c>
       <c r="B45" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5002,19 +4993,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5022,10 +5017,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434095</v>
+        <v>434679</v>
       </c>
       <c r="R45" t="n">
-        <v>7052227</v>
+        <v>7051828</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5058,6 +5053,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130886791</v>
+        <v>130886837</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5605,23 +5605,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5629,10 +5625,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434162</v>
+        <v>434513</v>
       </c>
       <c r="R51" t="n">
-        <v>7052153</v>
+        <v>7052004</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5665,11 +5661,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5696,7 +5687,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130886765</v>
+        <v>130886791</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -5731,10 +5722,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434505</v>
+        <v>434162</v>
       </c>
       <c r="R52" t="n">
-        <v>7052005</v>
+        <v>7052153</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5798,7 +5789,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130886788</v>
+        <v>130886765</v>
       </c>
       <c r="B53" t="n">
         <v>57884</v>
@@ -5833,10 +5824,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434171</v>
+        <v>434505</v>
       </c>
       <c r="R53" t="n">
-        <v>7052213</v>
+        <v>7052005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5873,7 +5864,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5900,7 +5891,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130886826</v>
+        <v>130886788</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -5935,10 +5926,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434489</v>
+        <v>434171</v>
       </c>
       <c r="R54" t="n">
-        <v>7051863</v>
+        <v>7052213</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6002,7 +5993,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130886811</v>
+        <v>130886826</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6037,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434077</v>
+        <v>434489</v>
       </c>
       <c r="R55" t="n">
-        <v>7052133</v>
+        <v>7051863</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6077,7 +6068,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6104,7 +6095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130886785</v>
+        <v>130886811</v>
       </c>
       <c r="B56" t="n">
         <v>57884</v>
@@ -6139,10 +6130,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434191</v>
+        <v>434077</v>
       </c>
       <c r="R56" t="n">
-        <v>7052193</v>
+        <v>7052133</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6179,7 +6170,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6206,10 +6197,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130886837</v>
+        <v>130886785</v>
       </c>
       <c r="B57" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6217,19 +6208,23 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6237,10 +6232,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434513</v>
+        <v>434191</v>
       </c>
       <c r="R57" t="n">
-        <v>7052004</v>
+        <v>7052193</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6273,6 +6268,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7829,27 +7829,27 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130886823</v>
+        <v>130886832</v>
       </c>
       <c r="B73" t="n">
-        <v>57884</v>
+        <v>57988</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7857,17 +7857,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434499</v>
+        <v>434123</v>
       </c>
       <c r="R73" t="n">
-        <v>7051916</v>
+        <v>7052111</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7900,11 +7916,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7931,7 +7942,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130886813</v>
+        <v>130886823</v>
       </c>
       <c r="B74" t="n">
         <v>57884</v>
@@ -7966,10 +7977,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434112</v>
+        <v>434499</v>
       </c>
       <c r="R74" t="n">
-        <v>7052117</v>
+        <v>7051916</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8033,7 +8044,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130886762</v>
+        <v>130886813</v>
       </c>
       <c r="B75" t="n">
         <v>57884</v>
@@ -8068,10 +8079,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434867</v>
+        <v>434112</v>
       </c>
       <c r="R75" t="n">
-        <v>7051762</v>
+        <v>7052117</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8108,7 +8119,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8135,7 +8146,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130886821</v>
+        <v>130886762</v>
       </c>
       <c r="B76" t="n">
         <v>57884</v>
@@ -8170,10 +8181,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434468</v>
+        <v>434867</v>
       </c>
       <c r="R76" t="n">
-        <v>7051906</v>
+        <v>7051762</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8237,7 +8248,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130886789</v>
+        <v>130886821</v>
       </c>
       <c r="B77" t="n">
         <v>57884</v>
@@ -8272,10 +8283,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434159</v>
+        <v>434468</v>
       </c>
       <c r="R77" t="n">
-        <v>7052197</v>
+        <v>7051906</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8339,27 +8350,27 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130886832</v>
+        <v>130886789</v>
       </c>
       <c r="B78" t="n">
-        <v>57988</v>
+        <v>57884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8367,33 +8378,17 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434123</v>
+        <v>434159</v>
       </c>
       <c r="R78" t="n">
-        <v>7052111</v>
+        <v>7052197</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8426,6 +8421,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD78" t="b">

--- a/artfynd/A 60977-2025 artfynd.xlsx
+++ b/artfynd/A 60977-2025 artfynd.xlsx
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130886838</v>
+        <v>130886779</v>
       </c>
       <c r="B11" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,19 +1559,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1579,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434362</v>
+        <v>434359</v>
       </c>
       <c r="R11" t="n">
-        <v>7052349</v>
+        <v>7052173</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1615,6 +1619,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1641,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130886779</v>
+        <v>130886838</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1652,23 +1661,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1676,10 +1681,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434359</v>
+        <v>434362</v>
       </c>
       <c r="R12" t="n">
-        <v>7052173</v>
+        <v>7052349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1712,11 +1717,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2660,10 +2660,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130886836</v>
+        <v>130886792</v>
       </c>
       <c r="B22" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2671,19 +2671,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2691,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434854</v>
+        <v>434158</v>
       </c>
       <c r="R22" t="n">
-        <v>7051718</v>
+        <v>7052168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2727,6 +2731,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2753,7 +2762,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130886792</v>
+        <v>130886801</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2788,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434158</v>
+        <v>434001</v>
       </c>
       <c r="R23" t="n">
-        <v>7052168</v>
+        <v>7052192</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,7 +2837,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2855,10 +2864,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130886801</v>
+        <v>130886836</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2866,23 +2875,19 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2890,10 +2895,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434001</v>
+        <v>434854</v>
       </c>
       <c r="R24" t="n">
-        <v>7052192</v>
+        <v>7051718</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2926,11 +2931,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130886835</v>
+        <v>130886825</v>
       </c>
       <c r="B38" t="n">
-        <v>91805</v>
+        <v>57884</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4302,21 +4302,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434666</v>
+        <v>434476</v>
       </c>
       <c r="R38" t="n">
-        <v>7051843</v>
+        <v>7051885</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,6 +4362,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4388,10 +4393,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130886845</v>
+        <v>130886805</v>
       </c>
       <c r="B39" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4399,19 +4404,23 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -4419,10 +4428,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434162</v>
+        <v>433991</v>
       </c>
       <c r="R39" t="n">
-        <v>7052165</v>
+        <v>7052188</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4455,6 +4464,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4481,10 +4495,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130886825</v>
+        <v>130886845</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4492,23 +4506,19 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4516,10 +4526,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434476</v>
+        <v>434162</v>
       </c>
       <c r="R40" t="n">
-        <v>7051885</v>
+        <v>7052165</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4552,11 +4562,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4583,10 +4588,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130886805</v>
+        <v>130886835</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>91805</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4594,21 +4599,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4618,10 +4623,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433991</v>
+        <v>434666</v>
       </c>
       <c r="R41" t="n">
-        <v>7052188</v>
+        <v>7051843</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4654,11 +4659,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4778,7 +4778,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130886786</v>
+        <v>130886828</v>
       </c>
       <c r="B43" t="n">
         <v>57884</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434196</v>
+        <v>434679</v>
       </c>
       <c r="R43" t="n">
-        <v>7052215</v>
+        <v>7051828</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4880,7 +4880,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130886798</v>
+        <v>130886786</v>
       </c>
       <c r="B44" t="n">
         <v>57884</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434094</v>
+        <v>434196</v>
       </c>
       <c r="R44" t="n">
-        <v>7052167</v>
+        <v>7052215</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4982,7 +4982,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130886828</v>
+        <v>130886798</v>
       </c>
       <c r="B45" t="n">
         <v>57884</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434679</v>
+        <v>434094</v>
       </c>
       <c r="R45" t="n">
-        <v>7051828</v>
+        <v>7052167</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5594,10 +5594,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130886837</v>
+        <v>130886791</v>
       </c>
       <c r="B51" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5605,19 +5605,23 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5625,10 +5629,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434513</v>
+        <v>434162</v>
       </c>
       <c r="R51" t="n">
-        <v>7052004</v>
+        <v>7052153</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5661,6 +5665,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5687,7 +5696,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130886791</v>
+        <v>130886765</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -5722,10 +5731,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434162</v>
+        <v>434505</v>
       </c>
       <c r="R52" t="n">
-        <v>7052153</v>
+        <v>7052005</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5789,7 +5798,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130886765</v>
+        <v>130886788</v>
       </c>
       <c r="B53" t="n">
         <v>57884</v>
@@ -5824,10 +5833,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434505</v>
+        <v>434171</v>
       </c>
       <c r="R53" t="n">
-        <v>7052005</v>
+        <v>7052213</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,7 +5873,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5891,7 +5900,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130886788</v>
+        <v>130886811</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -5926,10 +5935,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434171</v>
+        <v>434077</v>
       </c>
       <c r="R54" t="n">
-        <v>7052213</v>
+        <v>7052133</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5966,7 +5975,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5993,7 +6002,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130886826</v>
+        <v>130886785</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6028,10 +6037,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434489</v>
+        <v>434191</v>
       </c>
       <c r="R55" t="n">
-        <v>7051863</v>
+        <v>7052193</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6095,10 +6104,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130886811</v>
+        <v>130886837</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6106,23 +6115,19 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6130,10 +6135,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434077</v>
+        <v>434513</v>
       </c>
       <c r="R56" t="n">
-        <v>7052133</v>
+        <v>7052004</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6166,11 +6171,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130886785</v>
+        <v>130886826</v>
       </c>
       <c r="B57" t="n">
         <v>57884</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434191</v>
+        <v>434489</v>
       </c>
       <c r="R57" t="n">
-        <v>7052193</v>
+        <v>7051863</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130886829</v>
+        <v>130886803</v>
       </c>
       <c r="B67" t="n">
         <v>57884</v>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434697</v>
+        <v>433904</v>
       </c>
       <c r="R67" t="n">
-        <v>7051780</v>
+        <v>7052250</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7319,7 +7319,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130886803</v>
+        <v>130886829</v>
       </c>
       <c r="B68" t="n">
         <v>57884</v>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>433904</v>
+        <v>434697</v>
       </c>
       <c r="R68" t="n">
-        <v>7052250</v>
+        <v>7051780</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">

--- a/artfynd/A 60977-2025 artfynd.xlsx
+++ b/artfynd/A 60977-2025 artfynd.xlsx
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130886777</v>
+        <v>130886759</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -1967,16 +1967,24 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434295</v>
+        <v>434213</v>
       </c>
       <c r="R15" t="n">
-        <v>7052449</v>
+        <v>7052218</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2013,7 +2021,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2040,7 +2048,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130886759</v>
+        <v>130886777</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2069,24 +2077,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434213</v>
+        <v>434295</v>
       </c>
       <c r="R16" t="n">
-        <v>7052218</v>
+        <v>7052449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130886812</v>
+        <v>130886806</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434092</v>
+        <v>433991</v>
       </c>
       <c r="R18" t="n">
-        <v>7052113</v>
+        <v>7052181</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130886806</v>
+        <v>130886812</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433991</v>
+        <v>434092</v>
       </c>
       <c r="R19" t="n">
-        <v>7052181</v>
+        <v>7052113</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130886831</v>
+        <v>130886818</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>57884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,16 +2569,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434871</v>
+        <v>434272</v>
       </c>
       <c r="R21" t="n">
-        <v>7051709</v>
+        <v>7052031</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2660,7 +2660,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130886792</v>
+        <v>130886794</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -2695,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434158</v>
+        <v>434140</v>
       </c>
       <c r="R22" t="n">
-        <v>7052168</v>
+        <v>7052192</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2864,10 +2864,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130886836</v>
+        <v>130886793</v>
       </c>
       <c r="B24" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2875,19 +2875,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2895,10 +2899,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434854</v>
+        <v>434143</v>
       </c>
       <c r="R24" t="n">
-        <v>7051718</v>
+        <v>7052197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2931,6 +2935,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2957,7 +2966,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130886793</v>
+        <v>130886792</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -2992,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434143</v>
+        <v>434158</v>
       </c>
       <c r="R25" t="n">
-        <v>7052197</v>
+        <v>7052168</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130886794</v>
+        <v>130886836</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3070,23 +3079,19 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3094,10 +3099,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434140</v>
+        <v>434854</v>
       </c>
       <c r="R26" t="n">
-        <v>7052192</v>
+        <v>7051718</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,11 +3135,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3161,10 +3161,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130886818</v>
+        <v>130886831</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>57881</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3172,16 +3172,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434272</v>
+        <v>434871</v>
       </c>
       <c r="R27" t="n">
-        <v>7052031</v>
+        <v>7051709</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3569,7 +3569,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130886816</v>
+        <v>130886799</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434134</v>
+        <v>434100</v>
       </c>
       <c r="R31" t="n">
-        <v>7052114</v>
+        <v>7052230</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3773,7 +3773,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130886799</v>
+        <v>130886816</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434100</v>
+        <v>434134</v>
       </c>
       <c r="R33" t="n">
-        <v>7052230</v>
+        <v>7052114</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3875,7 +3875,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130886824</v>
+        <v>130886770</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434488</v>
+        <v>434510</v>
       </c>
       <c r="R34" t="n">
-        <v>7051909</v>
+        <v>7052005</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3977,7 +3977,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130886770</v>
+        <v>130886824</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434510</v>
+        <v>434488</v>
       </c>
       <c r="R35" t="n">
-        <v>7052005</v>
+        <v>7051909</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4778,7 +4778,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130886828</v>
+        <v>130886798</v>
       </c>
       <c r="B43" t="n">
         <v>57884</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434679</v>
+        <v>434094</v>
       </c>
       <c r="R43" t="n">
-        <v>7051828</v>
+        <v>7052167</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130886786</v>
+        <v>130886828</v>
       </c>
       <c r="B44" t="n">
         <v>57884</v>
@@ -4915,10 +4915,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434196</v>
+        <v>434679</v>
       </c>
       <c r="R44" t="n">
-        <v>7052215</v>
+        <v>7051828</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4982,7 +4982,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130886798</v>
+        <v>130886786</v>
       </c>
       <c r="B45" t="n">
         <v>57884</v>
@@ -5017,10 +5017,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434094</v>
+        <v>434196</v>
       </c>
       <c r="R45" t="n">
-        <v>7052167</v>
+        <v>7052215</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5186,7 +5186,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130886802</v>
+        <v>130886768</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434012</v>
+        <v>434508</v>
       </c>
       <c r="R47" t="n">
-        <v>7052200</v>
+        <v>7052004</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5390,7 +5390,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130886768</v>
+        <v>130886830</v>
       </c>
       <c r="B49" t="n">
         <v>57884</v>
@@ -5425,10 +5425,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434508</v>
+        <v>434860</v>
       </c>
       <c r="R49" t="n">
-        <v>7052004</v>
+        <v>7051773</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5492,7 +5492,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130886830</v>
+        <v>130886802</v>
       </c>
       <c r="B50" t="n">
         <v>57884</v>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434860</v>
+        <v>434012</v>
       </c>
       <c r="R50" t="n">
-        <v>7051773</v>
+        <v>7052200</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5594,10 +5594,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130886791</v>
+        <v>130886837</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>91829</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5605,23 +5605,19 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5629,10 +5625,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434162</v>
+        <v>434513</v>
       </c>
       <c r="R51" t="n">
-        <v>7052153</v>
+        <v>7052004</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5665,11 +5661,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5696,7 +5687,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130886765</v>
+        <v>130886826</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -5731,10 +5722,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434505</v>
+        <v>434489</v>
       </c>
       <c r="R52" t="n">
-        <v>7052005</v>
+        <v>7051863</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5771,7 +5762,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6002,7 +5993,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130886785</v>
+        <v>130886765</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6037,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434191</v>
+        <v>434505</v>
       </c>
       <c r="R55" t="n">
-        <v>7052193</v>
+        <v>7052005</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6077,7 +6068,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6104,10 +6095,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130886837</v>
+        <v>130886785</v>
       </c>
       <c r="B56" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6115,19 +6106,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434513</v>
+        <v>434191</v>
       </c>
       <c r="R56" t="n">
-        <v>7052004</v>
+        <v>7052193</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6171,6 +6166,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130886826</v>
+        <v>130886791</v>
       </c>
       <c r="B57" t="n">
         <v>57884</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434489</v>
+        <v>434162</v>
       </c>
       <c r="R57" t="n">
-        <v>7051863</v>
+        <v>7052153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6401,7 +6401,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130886815</v>
+        <v>130886781</v>
       </c>
       <c r="B59" t="n">
         <v>57884</v>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434133</v>
+        <v>434196</v>
       </c>
       <c r="R59" t="n">
-        <v>7052112</v>
+        <v>7052172</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6605,7 +6605,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130886781</v>
+        <v>130886815</v>
       </c>
       <c r="B61" t="n">
         <v>57884</v>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434196</v>
+        <v>434133</v>
       </c>
       <c r="R61" t="n">
-        <v>7052172</v>
+        <v>7052112</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130886803</v>
+        <v>130886829</v>
       </c>
       <c r="B67" t="n">
         <v>57884</v>
@@ -7252,10 +7252,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433904</v>
+        <v>434697</v>
       </c>
       <c r="R67" t="n">
-        <v>7052250</v>
+        <v>7051780</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7319,7 +7319,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130886829</v>
+        <v>130886803</v>
       </c>
       <c r="B68" t="n">
         <v>57884</v>
@@ -7354,10 +7354,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434697</v>
+        <v>433904</v>
       </c>
       <c r="R68" t="n">
-        <v>7051780</v>
+        <v>7052250</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7394,7 +7394,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7421,7 +7421,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130886819</v>
+        <v>130886807</v>
       </c>
       <c r="B69" t="n">
         <v>57884</v>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434379</v>
+        <v>434035</v>
       </c>
       <c r="R69" t="n">
-        <v>7051966</v>
+        <v>7052164</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7523,7 +7523,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130886807</v>
+        <v>130886819</v>
       </c>
       <c r="B70" t="n">
         <v>57884</v>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434035</v>
+        <v>434379</v>
       </c>
       <c r="R70" t="n">
-        <v>7052164</v>
+        <v>7051966</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8044,7 +8044,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130886813</v>
+        <v>130886762</v>
       </c>
       <c r="B75" t="n">
         <v>57884</v>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434112</v>
+        <v>434867</v>
       </c>
       <c r="R75" t="n">
-        <v>7052117</v>
+        <v>7051762</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8146,7 +8146,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130886762</v>
+        <v>130886821</v>
       </c>
       <c r="B76" t="n">
         <v>57884</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434867</v>
+        <v>434468</v>
       </c>
       <c r="R76" t="n">
-        <v>7051762</v>
+        <v>7051906</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8248,7 +8248,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130886821</v>
+        <v>130886813</v>
       </c>
       <c r="B77" t="n">
         <v>57884</v>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434468</v>
+        <v>434112</v>
       </c>
       <c r="R77" t="n">
-        <v>7051906</v>
+        <v>7052117</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 60977-2025 artfynd.xlsx
+++ b/artfynd/A 60977-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130886843</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -771,7 +771,7 @@
         <v>130886842</v>
       </c>
       <c r="B3" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>130886844</v>
       </c>
       <c r="B7" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>130886841</v>
       </c>
       <c r="B8" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>130886840</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>130886838</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>130886839</v>
       </c>
       <c r="B14" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130886759</v>
+        <v>130886777</v>
       </c>
       <c r="B15" t="n">
         <v>57884</v>
@@ -1967,24 +1967,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434213</v>
+        <v>434295</v>
       </c>
       <c r="R15" t="n">
-        <v>7052218</v>
+        <v>7052449</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2021,7 +2013,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,7 +2040,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130886777</v>
+        <v>130886759</v>
       </c>
       <c r="B16" t="n">
         <v>57884</v>
@@ -2077,16 +2069,24 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434295</v>
+        <v>434213</v>
       </c>
       <c r="R16" t="n">
-        <v>7052449</v>
+        <v>7052218</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2252,7 +2252,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130886806</v>
+        <v>130886812</v>
       </c>
       <c r="B18" t="n">
         <v>57884</v>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433991</v>
+        <v>434092</v>
       </c>
       <c r="R18" t="n">
-        <v>7052181</v>
+        <v>7052113</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,7 +2354,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130886812</v>
+        <v>130886806</v>
       </c>
       <c r="B19" t="n">
         <v>57884</v>
@@ -2389,10 +2389,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434092</v>
+        <v>433991</v>
       </c>
       <c r="R19" t="n">
-        <v>7052113</v>
+        <v>7052181</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130886818</v>
+        <v>130886792</v>
       </c>
       <c r="B21" t="n">
         <v>57884</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434272</v>
+        <v>434158</v>
       </c>
       <c r="R21" t="n">
-        <v>7052031</v>
+        <v>7052168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130886794</v>
+        <v>130886801</v>
       </c>
       <c r="B22" t="n">
         <v>57884</v>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434140</v>
+        <v>434001</v>
       </c>
       <c r="R22" t="n">
         <v>7052192</v>
@@ -2762,7 +2762,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130886801</v>
+        <v>130886793</v>
       </c>
       <c r="B23" t="n">
         <v>57884</v>
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434001</v>
+        <v>434143</v>
       </c>
       <c r="R23" t="n">
-        <v>7052192</v>
+        <v>7052197</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2864,7 +2864,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130886793</v>
+        <v>130886794</v>
       </c>
       <c r="B24" t="n">
         <v>57884</v>
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434143</v>
+        <v>434140</v>
       </c>
       <c r="R24" t="n">
-        <v>7052197</v>
+        <v>7052192</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2939,7 +2939,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2966,7 +2966,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130886792</v>
+        <v>130886818</v>
       </c>
       <c r="B25" t="n">
         <v>57884</v>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434158</v>
+        <v>434272</v>
       </c>
       <c r="R25" t="n">
-        <v>7052168</v>
+        <v>7052031</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3068,10 +3068,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130886836</v>
+        <v>130886831</v>
       </c>
       <c r="B26" t="n">
-        <v>91829</v>
+        <v>57881</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,19 +3079,23 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3099,10 +3103,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434854</v>
+        <v>434871</v>
       </c>
       <c r="R26" t="n">
-        <v>7051718</v>
+        <v>7051709</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,6 +3139,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3161,10 +3170,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130886831</v>
+        <v>130886836</v>
       </c>
       <c r="B27" t="n">
-        <v>57881</v>
+        <v>91830</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3172,23 +3181,19 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3196,10 +3201,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434871</v>
+        <v>434854</v>
       </c>
       <c r="R27" t="n">
-        <v>7051709</v>
+        <v>7051718</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3232,11 +3237,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Hack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3569,7 +3569,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130886799</v>
+        <v>130886816</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434100</v>
+        <v>434134</v>
       </c>
       <c r="R31" t="n">
-        <v>7052230</v>
+        <v>7052114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3773,7 +3773,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130886816</v>
+        <v>130886799</v>
       </c>
       <c r="B33" t="n">
         <v>57884</v>
@@ -3808,10 +3808,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434134</v>
+        <v>434100</v>
       </c>
       <c r="R33" t="n">
-        <v>7052114</v>
+        <v>7052230</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3875,7 +3875,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130886770</v>
+        <v>130886824</v>
       </c>
       <c r="B34" t="n">
         <v>57884</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434510</v>
+        <v>434488</v>
       </c>
       <c r="R34" t="n">
-        <v>7052005</v>
+        <v>7051909</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3950,7 +3950,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3977,7 +3977,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130886824</v>
+        <v>130886770</v>
       </c>
       <c r="B35" t="n">
         <v>57884</v>
@@ -4012,10 +4012,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434488</v>
+        <v>434510</v>
       </c>
       <c r="R35" t="n">
-        <v>7051909</v>
+        <v>7052005</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4291,10 +4291,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130886825</v>
+        <v>130886835</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>91806</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4302,21 +4302,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4326,10 +4326,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434476</v>
+        <v>434666</v>
       </c>
       <c r="R38" t="n">
-        <v>7051885</v>
+        <v>7051843</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,11 +4362,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4393,7 +4388,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130886805</v>
+        <v>130886825</v>
       </c>
       <c r="B39" t="n">
         <v>57884</v>
@@ -4428,10 +4423,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433991</v>
+        <v>434476</v>
       </c>
       <c r="R39" t="n">
-        <v>7052188</v>
+        <v>7051885</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4468,7 +4463,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4495,10 +4490,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130886845</v>
+        <v>130886805</v>
       </c>
       <c r="B40" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4506,19 +4501,23 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4526,10 +4525,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434162</v>
+        <v>433991</v>
       </c>
       <c r="R40" t="n">
-        <v>7052165</v>
+        <v>7052188</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4562,6 +4561,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4588,10 +4592,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130886835</v>
+        <v>130886845</v>
       </c>
       <c r="B41" t="n">
-        <v>91805</v>
+        <v>91830</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4599,23 +4603,19 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4623,10 +4623,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434666</v>
+        <v>434162</v>
       </c>
       <c r="R41" t="n">
-        <v>7051843</v>
+        <v>7052165</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4685,10 +4685,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130886846</v>
+        <v>130886786</v>
       </c>
       <c r="B42" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4696,19 +4696,23 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -4716,10 +4720,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434095</v>
+        <v>434196</v>
       </c>
       <c r="R42" t="n">
-        <v>7052227</v>
+        <v>7052215</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4752,6 +4756,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4982,10 +4991,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130886786</v>
+        <v>130886846</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>91830</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4993,23 +5002,19 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5017,10 +5022,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434196</v>
+        <v>434095</v>
       </c>
       <c r="R45" t="n">
-        <v>7052215</v>
+        <v>7052227</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5053,11 +5058,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5186,7 +5186,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130886768</v>
+        <v>130886802</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5221,10 +5221,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434508</v>
+        <v>434012</v>
       </c>
       <c r="R47" t="n">
-        <v>7052004</v>
+        <v>7052200</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5492,7 +5492,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130886802</v>
+        <v>130886768</v>
       </c>
       <c r="B50" t="n">
         <v>57884</v>
@@ -5527,10 +5527,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434012</v>
+        <v>434508</v>
       </c>
       <c r="R50" t="n">
-        <v>7052200</v>
+        <v>7052004</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5597,7 +5597,7 @@
         <v>130886837</v>
       </c>
       <c r="B51" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130886826</v>
+        <v>130886791</v>
       </c>
       <c r="B52" t="n">
         <v>57884</v>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434489</v>
+        <v>434162</v>
       </c>
       <c r="R52" t="n">
-        <v>7051863</v>
+        <v>7052153</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5789,7 +5789,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130886788</v>
+        <v>130886765</v>
       </c>
       <c r="B53" t="n">
         <v>57884</v>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434171</v>
+        <v>434505</v>
       </c>
       <c r="R53" t="n">
-        <v>7052213</v>
+        <v>7052005</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5891,7 +5891,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130886811</v>
+        <v>130886788</v>
       </c>
       <c r="B54" t="n">
         <v>57884</v>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434077</v>
+        <v>434171</v>
       </c>
       <c r="R54" t="n">
-        <v>7052133</v>
+        <v>7052213</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5993,7 +5993,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130886765</v>
+        <v>130886826</v>
       </c>
       <c r="B55" t="n">
         <v>57884</v>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434505</v>
+        <v>434489</v>
       </c>
       <c r="R55" t="n">
-        <v>7052005</v>
+        <v>7051863</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6068,7 +6068,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6095,7 +6095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130886785</v>
+        <v>130886811</v>
       </c>
       <c r="B56" t="n">
         <v>57884</v>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434191</v>
+        <v>434077</v>
       </c>
       <c r="R56" t="n">
-        <v>7052193</v>
+        <v>7052133</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6197,7 +6197,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130886791</v>
+        <v>130886785</v>
       </c>
       <c r="B57" t="n">
         <v>57884</v>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434162</v>
+        <v>434191</v>
       </c>
       <c r="R57" t="n">
-        <v>7052153</v>
+        <v>7052193</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,7 +6272,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6401,7 +6401,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130886781</v>
+        <v>130886815</v>
       </c>
       <c r="B59" t="n">
         <v>57884</v>
@@ -6436,10 +6436,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434196</v>
+        <v>434133</v>
       </c>
       <c r="R59" t="n">
-        <v>7052172</v>
+        <v>7052112</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6605,7 +6605,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130886815</v>
+        <v>130886781</v>
       </c>
       <c r="B61" t="n">
         <v>57884</v>
@@ -6640,10 +6640,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434133</v>
+        <v>434196</v>
       </c>
       <c r="R61" t="n">
-        <v>7052112</v>
+        <v>7052172</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7421,7 +7421,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130886807</v>
+        <v>130886819</v>
       </c>
       <c r="B69" t="n">
         <v>57884</v>
@@ -7456,10 +7456,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434035</v>
+        <v>434379</v>
       </c>
       <c r="R69" t="n">
-        <v>7052164</v>
+        <v>7051966</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7523,7 +7523,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130886819</v>
+        <v>130886807</v>
       </c>
       <c r="B70" t="n">
         <v>57884</v>
@@ -7558,10 +7558,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434379</v>
+        <v>434035</v>
       </c>
       <c r="R70" t="n">
-        <v>7051966</v>
+        <v>7052164</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8044,7 +8044,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130886762</v>
+        <v>130886813</v>
       </c>
       <c r="B75" t="n">
         <v>57884</v>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434867</v>
+        <v>434112</v>
       </c>
       <c r="R75" t="n">
-        <v>7051762</v>
+        <v>7052117</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8248,7 +8248,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130886813</v>
+        <v>130886789</v>
       </c>
       <c r="B77" t="n">
         <v>57884</v>
@@ -8283,10 +8283,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434112</v>
+        <v>434159</v>
       </c>
       <c r="R77" t="n">
-        <v>7052117</v>
+        <v>7052197</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8350,7 +8350,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130886789</v>
+        <v>130886762</v>
       </c>
       <c r="B78" t="n">
         <v>57884</v>
@@ -8385,10 +8385,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434159</v>
+        <v>434867</v>
       </c>
       <c r="R78" t="n">
-        <v>7052197</v>
+        <v>7051762</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>

--- a/artfynd/A 60977-2025 artfynd.xlsx
+++ b/artfynd/A 60977-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130886843</v>
+        <v>130886759</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,30 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>434321</v>
+        <v>434213</v>
       </c>
       <c r="R2" t="n">
-        <v>7052458</v>
+        <v>7052218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -742,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130886842</v>
+        <v>130886774</v>
       </c>
       <c r="B3" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -779,19 +796,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -799,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434316</v>
+        <v>434519</v>
       </c>
       <c r="R3" t="n">
-        <v>7052462</v>
+        <v>7052220</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -835,6 +856,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130886776</v>
+        <v>130886775</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434294</v>
+        <v>434302</v>
       </c>
       <c r="R4" t="n">
-        <v>7052466</v>
+        <v>7052481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -936,7 +962,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130886775</v>
+        <v>130886776</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -998,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434302</v>
+        <v>434294</v>
       </c>
       <c r="R5" t="n">
-        <v>7052481</v>
+        <v>7052466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1038,7 +1064,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1065,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130886780</v>
+        <v>130886777</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1100,10 +1126,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434348</v>
+        <v>434295</v>
       </c>
       <c r="R6" t="n">
-        <v>7052170</v>
+        <v>7052449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1140,7 +1166,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130886844</v>
+        <v>130886778</v>
       </c>
       <c r="B7" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1178,19 +1204,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1198,10 +1228,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434213</v>
+        <v>434304</v>
       </c>
       <c r="R7" t="n">
-        <v>7052219</v>
+        <v>7052300</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1234,6 +1264,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1260,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130886841</v>
+        <v>130886779</v>
       </c>
       <c r="B8" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1271,19 +1306,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1291,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>434309</v>
+        <v>434359</v>
       </c>
       <c r="R8" t="n">
-        <v>7052486</v>
+        <v>7052173</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1327,6 +1366,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1353,10 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130886840</v>
+        <v>130886780</v>
       </c>
       <c r="B9" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1364,19 +1408,23 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1384,10 +1432,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434309</v>
+        <v>434348</v>
       </c>
       <c r="R9" t="n">
-        <v>7052438</v>
+        <v>7052170</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1420,6 +1468,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1446,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130886778</v>
+        <v>130886835</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,21 +1510,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1481,10 +1534,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434304</v>
+        <v>434666</v>
       </c>
       <c r="R10" t="n">
-        <v>7052300</v>
+        <v>7051843</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1517,11 +1570,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,27 +1596,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130886779</v>
+        <v>130886831</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1631,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434359</v>
+        <v>434871</v>
       </c>
       <c r="R11" t="n">
-        <v>7052173</v>
+        <v>7051709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1623,7 +1671,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,10 +1698,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130886838</v>
+        <v>130886760</v>
       </c>
       <c r="B12" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,19 +1709,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1681,10 +1733,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434362</v>
+        <v>434866</v>
       </c>
       <c r="R12" t="n">
-        <v>7052349</v>
+        <v>7051708</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1717,6 +1769,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1743,10 +1800,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130886774</v>
+        <v>130886761</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1778,10 +1835,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434519</v>
+        <v>434829</v>
       </c>
       <c r="R13" t="n">
-        <v>7052220</v>
+        <v>7051724</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1818,7 +1875,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1845,10 +1902,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130886839</v>
+        <v>130886762</v>
       </c>
       <c r="B14" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,19 +1913,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1876,10 +1937,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434382</v>
+        <v>434867</v>
       </c>
       <c r="R14" t="n">
-        <v>7052442</v>
+        <v>7051762</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1912,6 +1973,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1938,10 +2004,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130886777</v>
+        <v>130886763</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1973,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434295</v>
+        <v>434642</v>
       </c>
       <c r="R15" t="n">
-        <v>7052449</v>
+        <v>7051990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,10 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130886759</v>
+        <v>130886765</v>
       </c>
       <c r="B16" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2069,24 +2135,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434213</v>
+        <v>434505</v>
       </c>
       <c r="R16" t="n">
-        <v>7052218</v>
+        <v>7052005</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2123,7 +2181,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gammalt bohål i grantickerötad gran. Troligen gjort av tretåig hackspett.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2208,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130886800</v>
+        <v>130886766</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2185,10 +2243,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434076</v>
+        <v>434506</v>
       </c>
       <c r="R17" t="n">
-        <v>7052252</v>
+        <v>7052005</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130886812</v>
+        <v>130886768</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2287,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434092</v>
+        <v>434508</v>
       </c>
       <c r="R18" t="n">
-        <v>7052113</v>
+        <v>7052004</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2327,7 +2385,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2354,10 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130886806</v>
+        <v>130886770</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2389,10 +2447,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433991</v>
+        <v>434510</v>
       </c>
       <c r="R19" t="n">
-        <v>7052181</v>
+        <v>7052005</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2456,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130886804</v>
+        <v>130886771</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2491,10 +2549,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433939</v>
+        <v>434495</v>
       </c>
       <c r="R20" t="n">
-        <v>7052224</v>
+        <v>7052002</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,7 +2589,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2558,10 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130886792</v>
+        <v>130886773</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2651,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434158</v>
+        <v>434554</v>
       </c>
       <c r="R21" t="n">
-        <v>7052168</v>
+        <v>7052008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2633,7 +2691,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2660,10 +2718,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130886801</v>
+        <v>130886781</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2695,10 +2753,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434001</v>
+        <v>434196</v>
       </c>
       <c r="R22" t="n">
-        <v>7052192</v>
+        <v>7052172</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2735,7 +2793,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2762,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130886793</v>
+        <v>130886782</v>
       </c>
       <c r="B23" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2797,10 +2855,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434143</v>
+        <v>434188</v>
       </c>
       <c r="R23" t="n">
-        <v>7052197</v>
+        <v>7052189</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2864,10 +2922,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130886794</v>
+        <v>130886785</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2899,10 +2957,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434140</v>
+        <v>434191</v>
       </c>
       <c r="R24" t="n">
-        <v>7052192</v>
+        <v>7052193</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2939,7 +2997,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2966,10 +3024,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130886818</v>
+        <v>130886786</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,10 +3059,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434272</v>
+        <v>434196</v>
       </c>
       <c r="R25" t="n">
-        <v>7052031</v>
+        <v>7052215</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3041,7 +3099,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3068,10 +3126,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130886831</v>
+        <v>130886787</v>
       </c>
       <c r="B26" t="n">
-        <v>57881</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3079,16 +3137,16 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3103,10 +3161,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434871</v>
+        <v>434193</v>
       </c>
       <c r="R26" t="n">
-        <v>7051709</v>
+        <v>7052219</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3143,7 +3201,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3170,10 +3228,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130886836</v>
+        <v>130886788</v>
       </c>
       <c r="B27" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3181,19 +3239,23 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3201,10 +3263,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434854</v>
+        <v>434171</v>
       </c>
       <c r="R27" t="n">
-        <v>7051718</v>
+        <v>7052213</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,6 +3299,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3263,10 +3330,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130886760</v>
+        <v>130886789</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3298,10 +3365,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434866</v>
+        <v>434159</v>
       </c>
       <c r="R28" t="n">
-        <v>7051708</v>
+        <v>7052197</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3365,10 +3432,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130886827</v>
+        <v>130886791</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3400,10 +3467,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434485</v>
+        <v>434162</v>
       </c>
       <c r="R29" t="n">
-        <v>7051846</v>
+        <v>7052153</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3467,10 +3534,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130886787</v>
+        <v>130886792</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434193</v>
+        <v>434158</v>
       </c>
       <c r="R30" t="n">
-        <v>7052219</v>
+        <v>7052168</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3569,10 +3636,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130886816</v>
+        <v>130886793</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3604,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434134</v>
+        <v>434143</v>
       </c>
       <c r="R31" t="n">
-        <v>7052114</v>
+        <v>7052197</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3671,10 +3738,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130886766</v>
+        <v>130886794</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3706,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434506</v>
+        <v>434140</v>
       </c>
       <c r="R32" t="n">
-        <v>7052005</v>
+        <v>7052192</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3746,7 +3813,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3773,10 +3840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130886799</v>
+        <v>130886795</v>
       </c>
       <c r="B33" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3808,10 +3875,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434100</v>
+        <v>434130</v>
       </c>
       <c r="R33" t="n">
-        <v>7052230</v>
+        <v>7052154</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3848,7 +3915,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3875,10 +3942,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130886824</v>
+        <v>130886796</v>
       </c>
       <c r="B34" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3910,10 +3977,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434488</v>
+        <v>434131</v>
       </c>
       <c r="R34" t="n">
-        <v>7051909</v>
+        <v>7052169</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3950,7 +4017,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3977,10 +4044,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130886770</v>
+        <v>130886797</v>
       </c>
       <c r="B35" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4012,10 +4079,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434510</v>
+        <v>434118</v>
       </c>
       <c r="R35" t="n">
-        <v>7052005</v>
+        <v>7052153</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4052,7 +4119,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4079,10 +4146,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130886822</v>
+        <v>130886798</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,24 +4175,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434465</v>
+        <v>434094</v>
       </c>
       <c r="R36" t="n">
-        <v>7051934</v>
+        <v>7052167</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4162,7 +4221,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Möjligt påbörjat gammalt bohål ca 1,7 m upp i rötad gran</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4189,10 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130886810</v>
+        <v>130886799</v>
       </c>
       <c r="B37" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4224,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434078</v>
+        <v>434100</v>
       </c>
       <c r="R37" t="n">
-        <v>7052137</v>
+        <v>7052230</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4264,7 +4323,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4291,10 +4350,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130886835</v>
+        <v>130886800</v>
       </c>
       <c r="B38" t="n">
-        <v>91806</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4302,21 +4361,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4326,10 +4385,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434666</v>
+        <v>434076</v>
       </c>
       <c r="R38" t="n">
-        <v>7051843</v>
+        <v>7052252</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4362,6 +4421,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4388,10 +4452,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130886825</v>
+        <v>130886801</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4423,10 +4487,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434476</v>
+        <v>434001</v>
       </c>
       <c r="R39" t="n">
-        <v>7051885</v>
+        <v>7052192</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4463,7 +4527,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4490,10 +4554,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130886805</v>
+        <v>130886802</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4525,10 +4589,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433991</v>
+        <v>434012</v>
       </c>
       <c r="R40" t="n">
-        <v>7052188</v>
+        <v>7052200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4565,7 +4629,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4592,10 +4656,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130886845</v>
+        <v>130886803</v>
       </c>
       <c r="B41" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,19 +4667,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -4623,10 +4691,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434162</v>
+        <v>433904</v>
       </c>
       <c r="R41" t="n">
-        <v>7052165</v>
+        <v>7052250</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4659,6 +4727,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4685,10 +4758,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130886786</v>
+        <v>130886804</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4720,10 +4793,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434196</v>
+        <v>433939</v>
       </c>
       <c r="R42" t="n">
-        <v>7052215</v>
+        <v>7052224</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,10 +4860,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130886798</v>
+        <v>130886805</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4822,10 +4895,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434094</v>
+        <v>433991</v>
       </c>
       <c r="R43" t="n">
-        <v>7052167</v>
+        <v>7052188</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4862,7 +4935,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4889,10 +4962,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130886828</v>
+        <v>130886806</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4924,10 +4997,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434679</v>
+        <v>433991</v>
       </c>
       <c r="R44" t="n">
-        <v>7051828</v>
+        <v>7052181</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4964,7 +5037,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4991,10 +5064,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130886846</v>
+        <v>130886807</v>
       </c>
       <c r="B45" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5002,19 +5075,23 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5022,10 +5099,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434095</v>
+        <v>434035</v>
       </c>
       <c r="R45" t="n">
-        <v>7052227</v>
+        <v>7052164</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5058,6 +5135,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5084,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130886763</v>
+        <v>130886808</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5119,10 +5201,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434642</v>
+        <v>434043</v>
       </c>
       <c r="R46" t="n">
-        <v>7051990</v>
+        <v>7052160</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5159,7 +5241,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5186,10 +5268,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130886802</v>
+        <v>130886810</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5221,10 +5303,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434012</v>
+        <v>434078</v>
       </c>
       <c r="R47" t="n">
-        <v>7052200</v>
+        <v>7052137</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5261,7 +5343,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5288,10 +5370,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130886773</v>
+        <v>130886811</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5323,10 +5405,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434554</v>
+        <v>434077</v>
       </c>
       <c r="R48" t="n">
-        <v>7052008</v>
+        <v>7052133</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5363,7 +5445,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5390,10 +5472,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130886830</v>
+        <v>130886812</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5425,10 +5507,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434860</v>
+        <v>434092</v>
       </c>
       <c r="R49" t="n">
-        <v>7051773</v>
+        <v>7052113</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5465,7 +5547,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5492,10 +5574,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130886768</v>
+        <v>130886813</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5527,10 +5609,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434508</v>
+        <v>434112</v>
       </c>
       <c r="R50" t="n">
-        <v>7052004</v>
+        <v>7052117</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5567,7 +5649,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5594,10 +5676,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130886837</v>
+        <v>130886814</v>
       </c>
       <c r="B51" t="n">
-        <v>91830</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5605,19 +5687,23 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -5625,10 +5711,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434513</v>
+        <v>434117</v>
       </c>
       <c r="R51" t="n">
-        <v>7052004</v>
+        <v>7052108</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5661,6 +5747,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5687,10 +5778,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130886791</v>
+        <v>130886815</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5722,10 +5813,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434162</v>
+        <v>434133</v>
       </c>
       <c r="R52" t="n">
-        <v>7052153</v>
+        <v>7052112</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5762,7 +5853,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5789,10 +5880,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130886765</v>
+        <v>130886816</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5824,10 +5915,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434505</v>
+        <v>434134</v>
       </c>
       <c r="R53" t="n">
-        <v>7052005</v>
+        <v>7052114</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5864,7 +5955,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5891,10 +5982,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130886788</v>
+        <v>130886817</v>
       </c>
       <c r="B54" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5926,10 +6017,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434171</v>
+        <v>434240</v>
       </c>
       <c r="R54" t="n">
-        <v>7052213</v>
+        <v>7052045</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5993,10 +6084,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130886826</v>
+        <v>130886818</v>
       </c>
       <c r="B55" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6028,10 +6119,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434489</v>
+        <v>434272</v>
       </c>
       <c r="R55" t="n">
-        <v>7051863</v>
+        <v>7052031</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6095,10 +6186,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130886811</v>
+        <v>130886819</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6130,10 +6221,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434077</v>
+        <v>434379</v>
       </c>
       <c r="R56" t="n">
-        <v>7052133</v>
+        <v>7051966</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6170,7 +6261,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6197,10 +6288,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130886785</v>
+        <v>130886820</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6232,10 +6323,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434191</v>
+        <v>434371</v>
       </c>
       <c r="R57" t="n">
-        <v>7052193</v>
+        <v>7051901</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6272,7 +6363,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6299,10 +6390,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130886771</v>
+        <v>130886821</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6334,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434495</v>
+        <v>434468</v>
       </c>
       <c r="R58" t="n">
-        <v>7052002</v>
+        <v>7051906</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6401,10 +6492,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130886815</v>
+        <v>130886822</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6430,16 +6521,24 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434133</v>
+        <v>434465</v>
       </c>
       <c r="R59" t="n">
-        <v>7052112</v>
+        <v>7051934</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6476,7 +6575,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Möjligt påbörjat gammalt bohål ca 1,7 m upp i rötad gran</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6503,10 +6602,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130886814</v>
+        <v>130886823</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6538,10 +6637,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434117</v>
+        <v>434499</v>
       </c>
       <c r="R60" t="n">
-        <v>7052108</v>
+        <v>7051916</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6605,10 +6704,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130886781</v>
+        <v>130886824</v>
       </c>
       <c r="B61" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6640,10 +6739,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434196</v>
+        <v>434488</v>
       </c>
       <c r="R61" t="n">
-        <v>7052172</v>
+        <v>7051909</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6707,10 +6806,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130886817</v>
+        <v>130886825</v>
       </c>
       <c r="B62" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6742,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434240</v>
+        <v>434476</v>
       </c>
       <c r="R62" t="n">
-        <v>7052045</v>
+        <v>7051885</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6809,10 +6908,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130886782</v>
+        <v>130886826</v>
       </c>
       <c r="B63" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6844,10 +6943,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434188</v>
+        <v>434489</v>
       </c>
       <c r="R63" t="n">
-        <v>7052189</v>
+        <v>7051863</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6911,10 +7010,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130886797</v>
+        <v>130886827</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6946,10 +7045,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434118</v>
+        <v>434485</v>
       </c>
       <c r="R64" t="n">
-        <v>7052153</v>
+        <v>7051846</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6986,7 +7085,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7013,10 +7112,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130886808</v>
+        <v>130886828</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7048,10 +7147,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434043</v>
+        <v>434679</v>
       </c>
       <c r="R65" t="n">
-        <v>7052160</v>
+        <v>7051828</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7088,7 +7187,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7115,10 +7214,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130886795</v>
+        <v>130886829</v>
       </c>
       <c r="B66" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7150,10 +7249,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434130</v>
+        <v>434697</v>
       </c>
       <c r="R66" t="n">
-        <v>7052154</v>
+        <v>7051780</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7190,7 +7289,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7217,10 +7316,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130886829</v>
+        <v>130886830</v>
       </c>
       <c r="B67" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7252,10 +7351,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434697</v>
+        <v>434860</v>
       </c>
       <c r="R67" t="n">
-        <v>7051780</v>
+        <v>7051773</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7292,7 +7391,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7319,10 +7418,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130886803</v>
+        <v>130886832</v>
       </c>
       <c r="B68" t="n">
-        <v>57884</v>
+        <v>58057</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7330,16 +7429,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7347,17 +7446,33 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Rävlungerflon, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>433904</v>
+        <v>434123</v>
       </c>
       <c r="R68" t="n">
-        <v>7052250</v>
+        <v>7052111</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7392,11 +7507,6 @@
           <t>2026-01-26</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7418,1037 +7528,6 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>130886819</v>
-      </c>
-      <c r="B69" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>434379</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7051966</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>130886807</v>
-      </c>
-      <c r="B70" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>434035</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7052164</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>130886796</v>
-      </c>
-      <c r="B71" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>434131</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7052169</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>130886761</v>
-      </c>
-      <c r="B72" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>434829</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7051724</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>130886832</v>
-      </c>
-      <c r="B73" t="n">
-        <v>57988</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>434123</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7052111</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>130886823</v>
-      </c>
-      <c r="B74" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>434499</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7051916</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>130886813</v>
-      </c>
-      <c r="B75" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>434112</v>
-      </c>
-      <c r="R75" t="n">
-        <v>7052117</v>
-      </c>
-      <c r="S75" t="n">
-        <v>10</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>130886821</v>
-      </c>
-      <c r="B76" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>434468</v>
-      </c>
-      <c r="R76" t="n">
-        <v>7051906</v>
-      </c>
-      <c r="S76" t="n">
-        <v>10</v>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V76" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W76" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y76" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>130886789</v>
-      </c>
-      <c r="B77" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>434159</v>
-      </c>
-      <c r="R77" t="n">
-        <v>7052197</v>
-      </c>
-      <c r="S77" t="n">
-        <v>10</v>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>130886762</v>
-      </c>
-      <c r="B78" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Rävlungerflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q78" t="n">
-        <v>434867</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7051762</v>
-      </c>
-      <c r="S78" t="n">
-        <v>10</v>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y78" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
-      <c r="AD78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60977-2025 artfynd.xlsx
+++ b/artfynd/A 60977-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AZ68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886759</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886774</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886775</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1190,6 +1215,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886777</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886778</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886779</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1496,6 +1536,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886780</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886835</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886831</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1797,6 +1852,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886760</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886761</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886762</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2103,6 +2173,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886763</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2205,6 +2280,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886765</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2307,6 +2387,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886766</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886768</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2511,6 +2601,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886770</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2613,6 +2708,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886771</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2715,6 +2815,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886773</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2817,6 +2922,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886817</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2919,6 +3029,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886818</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3021,6 +3136,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886819</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3123,6 +3243,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886820</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3225,6 +3350,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886821</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3335,6 +3465,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886822</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3437,6 +3572,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886823</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3539,6 +3679,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886824</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3641,6 +3786,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886825</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3743,6 +3893,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886826</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3845,6 +4000,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886827</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3947,6 +4107,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886828</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4049,6 +4214,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886829</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4151,6 +4321,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886830</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4253,6 +4428,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886781</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4355,6 +4535,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886782</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4457,6 +4642,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886785</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4559,6 +4749,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886786</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4661,6 +4856,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886787</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4763,6 +4963,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886788</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4865,6 +5070,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886789</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4967,6 +5177,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886791</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5069,6 +5284,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886792</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5171,6 +5391,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886793</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5273,6 +5498,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886794</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5375,6 +5605,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886795</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5477,6 +5712,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886796</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5579,6 +5819,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886797</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5681,6 +5926,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886798</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5783,6 +6033,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886799</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5885,6 +6140,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886800</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5987,6 +6247,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886801</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6089,6 +6354,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886802</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6191,6 +6461,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886803</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6293,6 +6568,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886804</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6395,6 +6675,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886805</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6497,6 +6782,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886806</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6599,6 +6889,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886807</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6701,6 +6996,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886808</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6803,6 +7103,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886810</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6905,6 +7210,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886811</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7007,6 +7317,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886812</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7109,6 +7424,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886813</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7211,6 +7531,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886814</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7313,6 +7638,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886815</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7415,6 +7745,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886816</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7528,8 +7863,82 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130886832</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>